--- a/public/downloads/ZhangUnlocking2025.xlsx
+++ b/public/downloads/ZhangUnlocking2025.xlsx
@@ -1626,16 +1626,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0695456400647666</v>
+        <v>0.266323461870356</v>
       </c>
       <c r="O3" s="5">
         <v>142</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5873096535813507</v>
+        <v>0.5735366580233434</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5117612215793412</v>
+        <v>0.5059320843952447</v>
       </c>
       <c r="R3" s="5">
         <v>140</v>
@@ -1685,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6157438482969745</v>
+        <v>-0.4920490473170691</v>
       </c>
       <c r="O4" s="5">
         <v>85</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9198048160754789</v>
+        <v>0.8922754595049919</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4417649872189145</v>
+        <v>0.4373992883608029</v>
       </c>
       <c r="R4" s="5">
         <v>85</v>
@@ -1744,16 +1744,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5663497895228208</v>
+        <v>-0.5464726736091734</v>
       </c>
       <c r="O5" s="5">
         <v>145</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4225906304883726</v>
+        <v>0.4175424195234647</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2276830085537881</v>
+        <v>0.2268277982985237</v>
       </c>
       <c r="R5" s="5">
         <v>145</v>
@@ -1803,16 +1803,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3010606871763218</v>
+        <v>-0.2880074362475824</v>
       </c>
       <c r="O6" s="5">
         <v>161</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2775467045473337</v>
+        <v>0.2771511514888871</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2612310334307124</v>
+        <v>0.2611499573379873</v>
       </c>
       <c r="R6" s="5">
         <v>161</v>
@@ -1862,16 +1862,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.0796573539215049</v>
+        <v>-0.09521992025507675</v>
       </c>
       <c r="O7" s="5">
         <v>159</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1954533515519231</v>
+        <v>0.1951486339315763</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1907267710289128</v>
+        <v>0.1903145933177779</v>
       </c>
       <c r="R7" s="5">
         <v>159</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1547269766820105</v>
+        <v>-0.291904035789317</v>
       </c>
       <c r="O8" s="5">
         <v>99</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4503889626378587</v>
+        <v>0.4801669369989017</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3282409714064076</v>
+        <v>0.3064551212531134</v>
       </c>
       <c r="R8" s="5">
         <v>99</v>
@@ -1980,16 +1980,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>1.545888881193075</v>
+        <v>1.451824079819035</v>
       </c>
       <c r="O9" s="5">
         <v>13</v>
       </c>
       <c r="P9" s="4">
-        <v>1.178256238277247</v>
+        <v>1.183789461887484</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2470202951737024</v>
+        <v>0.2253130333181548</v>
       </c>
       <c r="R9" s="5">
         <v>13</v>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.7350882730824745</v>
+        <v>0.6670575413529471</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.5440064040262611</v>
+        <v>0.538291027918458</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1301849137327531</v>
+        <v>0.1136657011765351</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -2221,16 +2221,16 @@
         <v>60</v>
       </c>
       <c r="N3" s="4">
-        <v>-2.253266669166558</v>
+        <v>-2.383784600163896</v>
       </c>
       <c r="O3" s="5">
         <v>87</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5716285788995256</v>
+        <v>0.5894256924250273</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4134500475353501</v>
+        <v>0.4008112142712659</v>
       </c>
       <c r="R3" s="5">
         <v>87</v>
@@ -2280,22 +2280,22 @@
         <v>84</v>
       </c>
       <c r="N4" s="4">
-        <v>-3.332993486413059</v>
+        <v>-3.107940728573063</v>
       </c>
       <c r="O4" s="5">
         <v>99</v>
       </c>
       <c r="P4" s="4">
-        <v>1.264640281224421</v>
+        <v>1.238139800964289</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8346588609530954</v>
+        <v>0.9478080417182125</v>
       </c>
       <c r="R4" s="5">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="S4" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2339,16 +2339,16 @@
         <v>37</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.538763585366076</v>
+        <v>-1.554931955506987</v>
       </c>
       <c r="O5" s="5">
         <v>114</v>
       </c>
       <c r="P5" s="4">
-        <v>0.595318609023903</v>
+        <v>0.5955861818053491</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3735758428380316</v>
+        <v>0.3730146919208862</v>
       </c>
       <c r="R5" s="5">
         <v>113</v>
@@ -2398,16 +2398,16 @@
         <v>104</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.461071467706202</v>
+        <v>-2.424203966864082</v>
       </c>
       <c r="O6" s="5">
         <v>143</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4973695428323004</v>
+        <v>0.4921079428781552</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4374410145695357</v>
+        <v>0.4360009644340431</v>
       </c>
       <c r="R6" s="5">
         <v>143</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.154851147710456</v>
+        <v>-1.145834024385522</v>
       </c>
       <c r="O7" s="5">
         <v>141</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2786975318986369</v>
+        <v>0.2786949591981138</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1777367077149754</v>
+        <v>0.1775418616663187</v>
       </c>
       <c r="R7" s="5">
         <v>141</v>
@@ -2516,16 +2516,16 @@
         <v>78</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.302414113325867</v>
+        <v>-2.233383232784234</v>
       </c>
       <c r="O8" s="5">
         <v>106</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5763072620479897</v>
+        <v>0.5723053292717084</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4141112694034597</v>
+        <v>0.4132804939329697</v>
       </c>
       <c r="R8" s="5">
         <v>106</v>
@@ -2628,16 +2628,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.441689751980082</v>
+        <v>-0.4069166445428891</v>
       </c>
       <c r="O10" s="5">
         <v>16</v>
       </c>
       <c r="P10" s="4">
-        <v>0.09721451830515759</v>
+        <v>0.09516904139708743</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08662966254204862</v>
+        <v>0.08228302411239952</v>
       </c>
       <c r="R10" s="5">
         <v>16</v>
@@ -2810,16 +2810,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.8641157509947707</v>
+        <v>0.9152879116269739</v>
       </c>
       <c r="O3" s="5">
         <v>176</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5607490754101725</v>
+        <v>0.5581416899307697</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4524023945316454</v>
+        <v>0.4506070741438034</v>
       </c>
       <c r="R3" s="5">
         <v>175</v>
@@ -2869,16 +2869,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7060187051731466</v>
+        <v>0.6737564712066195</v>
       </c>
       <c r="O4" s="5">
         <v>144</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7412873283608302</v>
+        <v>0.7391291501971272</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4277993039332038</v>
+        <v>0.425639505731131</v>
       </c>
       <c r="R4" s="5">
         <v>140</v>
@@ -2928,16 +2928,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3374646069208118</v>
+        <v>0.3142789767685485</v>
       </c>
       <c r="O5" s="5">
         <v>146</v>
       </c>
       <c r="P5" s="4">
-        <v>0.381476928274081</v>
+        <v>0.3798077684702685</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.340815095450561</v>
+        <v>0.3398538844970215</v>
       </c>
       <c r="R5" s="5">
         <v>143</v>
@@ -2987,16 +2987,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1058376874912474</v>
+        <v>0.08581809388536055</v>
       </c>
       <c r="O6" s="5">
         <v>130</v>
       </c>
       <c r="P6" s="4">
-        <v>0.339197030312355</v>
+        <v>0.3372950462318295</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2966152893664645</v>
+        <v>0.2963669342506806</v>
       </c>
       <c r="R6" s="5">
         <v>130</v>
@@ -3046,16 +3046,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2529258786407666</v>
+        <v>0.2221176072459503</v>
       </c>
       <c r="O7" s="5">
         <v>139</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2524317612618969</v>
+        <v>0.2514440113111595</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2457697077753259</v>
+        <v>0.2445051082272869</v>
       </c>
       <c r="R7" s="5">
         <v>139</v>
@@ -3105,16 +3105,16 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>0.5028828739330674</v>
+        <v>0.4121303253272437</v>
       </c>
       <c r="O8" s="5">
         <v>139</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4794321027132663</v>
+        <v>0.4672285708511281</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3832108124045069</v>
+        <v>0.3681594992951066</v>
       </c>
       <c r="R8" s="5">
         <v>136</v>
@@ -3164,16 +3164,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.6620858163301582</v>
+        <v>0.5964615669864246</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3439878712962464</v>
+        <v>0.3324072018032577</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3439878712962464</v>
+        <v>0.3324072018032577</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -3223,16 +3223,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1867839653330042</v>
+        <v>0.1149456250800847</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.147311027413473</v>
+        <v>0.1415593101816094</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.108896015417256</v>
+        <v>0.08847724817331387</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
@@ -3405,16 +3405,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07852762622360801</v>
+        <v>0.01261780581937</v>
       </c>
       <c r="O3" s="5">
         <v>169</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5226089399381196</v>
+        <v>0.5286267036997481</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3824927647920071</v>
+        <v>0.3788405235968721</v>
       </c>
       <c r="R3" s="5">
         <v>165</v>
@@ -3464,16 +3464,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3481970879569539</v>
+        <v>-0.6773733066071177</v>
       </c>
       <c r="O4" s="5">
         <v>58</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8410825082702396</v>
+        <v>0.9911775897927618</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.49995054969109</v>
+        <v>0.4073976182098409</v>
       </c>
       <c r="R4" s="5">
         <v>55</v>
@@ -3523,16 +3523,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.02023207596863385</v>
+        <v>0.01999220746318997</v>
       </c>
       <c r="O5" s="5">
         <v>163</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5778165989616982</v>
+        <v>0.5721393757063599</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3806061649861076</v>
+        <v>0.3798036802832794</v>
       </c>
       <c r="R5" s="5">
         <v>163</v>
@@ -3582,16 +3582,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.550620876725884</v>
+        <v>-0.6550700350818488</v>
       </c>
       <c r="O6" s="5">
         <v>163</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2553543052067344</v>
+        <v>0.2329163842296181</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2274809959444672</v>
+        <v>0.2018906009466532</v>
       </c>
       <c r="R6" s="5">
         <v>161</v>
@@ -3641,16 +3641,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4102909313427769</v>
+        <v>-0.4705157647193987</v>
       </c>
       <c r="O7" s="5">
         <v>162</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2359940857645085</v>
+        <v>0.2316777606044204</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2241066614463681</v>
+        <v>0.2185877060029873</v>
       </c>
       <c r="R7" s="5">
         <v>161</v>
@@ -3700,22 +3700,22 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>0.3186327301848181</v>
+        <v>0.3703760190358789</v>
       </c>
       <c r="O8" s="5">
         <v>22</v>
       </c>
       <c r="P8" s="4">
-        <v>1.337104133720573</v>
+        <v>1.372678387471068</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.5883552075898827</v>
+        <v>0.6436845991028846</v>
       </c>
       <c r="R8" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
@@ -3812,16 +3812,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.122669455232525</v>
+        <v>-0.03731077455686727</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3255879973082462</v>
+        <v>0.286169913447617</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.3269833744340925</v>
+        <v>0.292570101615386</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
@@ -3994,16 +3994,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2669322460968033</v>
+        <v>0.2338498487627683</v>
       </c>
       <c r="O3" s="5">
         <v>174</v>
       </c>
       <c r="P3" s="4">
-        <v>1.025815016620895</v>
+        <v>1.024932126803018</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3787081164740623</v>
+        <v>0.3764939776707381</v>
       </c>
       <c r="R3" s="5">
         <v>169</v>
@@ -4053,16 +4053,16 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2013364257618875</v>
+        <v>0.08499468050807923</v>
       </c>
       <c r="O4" s="5">
         <v>160</v>
       </c>
       <c r="P4" s="4">
-        <v>1.404057207905922</v>
+        <v>1.387870501393887</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5293527103208532</v>
+        <v>0.5068474222705867</v>
       </c>
       <c r="R4" s="5">
         <v>149</v>
@@ -4112,16 +4112,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1460322694365842</v>
+        <v>0.09258801816167761</v>
       </c>
       <c r="O5" s="5">
         <v>169</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8429315646196232</v>
+        <v>0.8371862748022934</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3265728528350575</v>
+        <v>0.3215775463041544</v>
       </c>
       <c r="R5" s="5">
         <v>166</v>
@@ -4171,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.547231821506258</v>
+        <v>-0.5534520052767675</v>
       </c>
       <c r="O6" s="5">
         <v>155</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5319787406620498</v>
+        <v>0.5317148540778464</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2329780975028581</v>
+        <v>0.2329379672849839</v>
       </c>
       <c r="R6" s="5">
         <v>155</v>
@@ -4230,22 +4230,22 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.203828213367401</v>
+        <v>-0.1981790639107053</v>
       </c>
       <c r="O7" s="5">
         <v>159</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2886325422234119</v>
+        <v>0.2887014881719127</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2063088551790422</v>
+        <v>0.2175020030297251</v>
       </c>
       <c r="R7" s="5">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -4289,16 +4289,16 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.02831530445475192</v>
+        <v>-0.1450770880146974</v>
       </c>
       <c r="O8" s="5">
         <v>146</v>
       </c>
       <c r="P8" s="4">
-        <v>0.8529387689883304</v>
+        <v>0.838780067460152</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3596689017204055</v>
+        <v>0.3446435138816041</v>
       </c>
       <c r="R8" s="5">
         <v>143</v>
@@ -4346,13 +4346,13 @@
         <v>12</v>
       </c>
       <c r="N9" s="4">
-        <v>5.09419880502007</v>
+        <v>5.008098349285159</v>
       </c>
       <c r="O9" s="5">
         <v>12</v>
       </c>
       <c r="P9" s="4">
-        <v>0.6793931285649562</v>
+        <v>0.6844578612552451</v>
       </c>
       <c r="Q9" s="4">
         <v>0.6484362881470016</v>
@@ -4405,16 +4405,16 @@
         <v>1</v>
       </c>
       <c r="N10" s="4">
-        <v>0.9164014712782655</v>
+        <v>0.7288883858771746</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.6020513808677345</v>
+        <v>0.5777902155490849</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.3191946912447551</v>
+        <v>0.2276300954864454</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -4587,16 +4587,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>1.094457827124406</v>
+        <v>1.138133022119347</v>
       </c>
       <c r="O3" s="5">
         <v>168</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5669761041884023</v>
+        <v>0.5602437789946924</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4821273841725793</v>
+        <v>0.480732553444343</v>
       </c>
       <c r="R3" s="5">
         <v>166</v>
@@ -4646,16 +4646,16 @@
         <v>17</v>
       </c>
       <c r="N4" s="4">
-        <v>1.227079620106156</v>
+        <v>1.097406614922088</v>
       </c>
       <c r="O4" s="5">
         <v>126</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8610351383736909</v>
+        <v>0.8602503009029153</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6118225985765645</v>
+        <v>0.5913947436303417</v>
       </c>
       <c r="R4" s="5">
         <v>116</v>
@@ -4705,16 +4705,16 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6999810445439179</v>
+        <v>0.6814326118549916</v>
       </c>
       <c r="O5" s="5">
         <v>180</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5473148576485177</v>
+        <v>0.5473414321469267</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4248605347864357</v>
+        <v>0.4241468423743305</v>
       </c>
       <c r="R5" s="5">
         <v>175</v>
@@ -4764,16 +4764,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.09705586810150124</v>
+        <v>0.06302990996596236</v>
       </c>
       <c r="O6" s="5">
         <v>165</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2865348769961743</v>
+        <v>0.2843940805073424</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2528402614567861</v>
+        <v>0.2502557011075325</v>
       </c>
       <c r="R6" s="5">
         <v>163</v>
@@ -4823,16 +4823,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2512182607222125</v>
+        <v>0.1827431567574345</v>
       </c>
       <c r="O7" s="5">
         <v>164</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2245264912383096</v>
+        <v>0.2156700468722812</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2098941634523007</v>
+        <v>0.2005632924093961</v>
       </c>
       <c r="R7" s="5">
         <v>163</v>
@@ -4882,16 +4882,16 @@
         <v>4</v>
       </c>
       <c r="N8" s="4">
-        <v>0.4169458603583864</v>
+        <v>0.2214862800752444</v>
       </c>
       <c r="O8" s="5">
         <v>102</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5463395072247127</v>
+        <v>0.4842974130445302</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4070741618819255</v>
+        <v>0.3610139958350639</v>
       </c>
       <c r="R8" s="5">
         <v>98</v>
@@ -4939,16 +4939,16 @@
         <v>17</v>
       </c>
       <c r="N9" s="4">
-        <v>3.140247147934698</v>
+        <v>3.358342494381513</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3541744650425462</v>
+        <v>0.3399652490949183</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3541744650425462</v>
+        <v>0.3399652490949183</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -4996,16 +4996,16 @@
         <v>10</v>
       </c>
       <c r="N10" s="4">
-        <v>2.527455339162478</v>
+        <v>2.567116467269064</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3143396789625408</v>
+        <v>0.3260842905131609</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1308337249196803</v>
+        <v>0.1230367748811243</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -5178,16 +5178,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03974875640927135</v>
+        <v>-0.04072195918726873</v>
       </c>
       <c r="O3" s="5">
         <v>168</v>
       </c>
       <c r="P3" s="4">
-        <v>0.473327987210367</v>
+        <v>0.4733035348792615</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3360652376755371</v>
+        <v>0.3360535123408624</v>
       </c>
       <c r="R3" s="5">
         <v>166</v>
@@ -5237,16 +5237,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1306492337192021</v>
+        <v>-0.209742149581734</v>
       </c>
       <c r="O4" s="5">
         <v>146</v>
       </c>
       <c r="P4" s="4">
-        <v>0.667129510093074</v>
+        <v>0.6724291164455697</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3906851655729796</v>
+        <v>0.3841780106213691</v>
       </c>
       <c r="R4" s="5">
         <v>141</v>
@@ -5296,16 +5296,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1338776025724696</v>
+        <v>0.1444720584079846</v>
       </c>
       <c r="O5" s="5">
         <v>171</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5811169914364277</v>
+        <v>0.5807078267069541</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4233661445008904</v>
+        <v>0.4232292666280826</v>
       </c>
       <c r="R5" s="5">
         <v>169</v>
@@ -5355,16 +5355,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7105120798449635</v>
+        <v>-0.7968599014052771</v>
       </c>
       <c r="O6" s="5">
         <v>160</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2051634353199727</v>
+        <v>0.1897646121429474</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1835617555905207</v>
+        <v>0.1669342008704607</v>
       </c>
       <c r="R6" s="5">
         <v>158</v>
@@ -5414,16 +5414,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.29682107070028</v>
+        <v>-0.3783247250173516</v>
       </c>
       <c r="O7" s="5">
         <v>160</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2253330535510211</v>
+        <v>0.215809489103615</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2165483605965539</v>
+        <v>0.206212711390946</v>
       </c>
       <c r="R7" s="5">
         <v>159</v>
@@ -5473,16 +5473,16 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1971825216833102</v>
+        <v>-0.2399793436314948</v>
       </c>
       <c r="O8" s="5">
         <v>134</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4000097930713992</v>
+        <v>0.3961110148812235</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2873842984922209</v>
+        <v>0.2817082630580784</v>
       </c>
       <c r="R8" s="5">
         <v>131</v>
@@ -5761,13 +5761,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9285205232797932</v>
+        <v>0.9259226836792491</v>
       </c>
       <c r="O3" s="5">
         <v>196</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3485800267276159</v>
+        <v>0.3485669722572615</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3516675398511962</v>
@@ -5820,16 +5820,16 @@
         <v>13</v>
       </c>
       <c r="N4" s="4">
-        <v>1.154081205890058</v>
+        <v>1.074714021272807</v>
       </c>
       <c r="O4" s="5">
         <v>164</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4276492065104608</v>
+        <v>0.4237411272653206</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.41315278036052</v>
+        <v>0.4084344895645584</v>
       </c>
       <c r="R4" s="5">
         <v>164</v>
@@ -5879,16 +5879,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4614792490430524</v>
+        <v>0.4692565711791303</v>
       </c>
       <c r="O5" s="5">
         <v>185</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2990923530709111</v>
+        <v>0.2989850270226778</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2990206524591074</v>
+        <v>0.2989547858491867</v>
       </c>
       <c r="R5" s="5">
         <v>185</v>
@@ -5938,16 +5938,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.7580575702374309</v>
+        <v>0.7385279021289648</v>
       </c>
       <c r="O6" s="5">
         <v>165</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1398643945047148</v>
+        <v>0.1389416410343627</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1398643945047148</v>
+        <v>0.1389416410343627</v>
       </c>
       <c r="R6" s="5">
         <v>165</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2997622596909569</v>
+        <v>0.2571493830554112</v>
       </c>
       <c r="O7" s="5">
         <v>164</v>
       </c>
       <c r="P7" s="4">
-        <v>0.213764432732338</v>
+        <v>0.2112952721407683</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.213764432732338</v>
+        <v>0.2112952721407683</v>
       </c>
       <c r="R7" s="5">
         <v>164</v>
@@ -6056,16 +6056,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>0.8005051475591148</v>
+        <v>0.8048945180306513</v>
       </c>
       <c r="O8" s="5">
         <v>159</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2524842756416087</v>
+        <v>0.2523630190460978</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2531895118313384</v>
+        <v>0.2530950987193245</v>
       </c>
       <c r="R8" s="5">
         <v>159</v>
@@ -6115,16 +6115,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.8467022871067501</v>
+        <v>0.7721043888191392</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1815897452501091</v>
+        <v>0.1763806171703003</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1815897452501091</v>
+        <v>0.1763806171703003</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -6174,16 +6174,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4344356531622481</v>
+        <v>0.4135132232394314</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1017403517875602</v>
+        <v>0.1043380306822361</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05960414432975021</v>
+        <v>0.05799472664337971</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
@@ -6356,16 +6356,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2573765477860384</v>
+        <v>-0.2540768738832475</v>
       </c>
       <c r="O3" s="5">
         <v>193</v>
       </c>
       <c r="P3" s="4">
-        <v>0.339457922655354</v>
+        <v>0.3393751309923595</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2608848791398822</v>
+        <v>0.260884999290293</v>
       </c>
       <c r="R3" s="5">
         <v>190</v>
@@ -6415,16 +6415,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2090557806705317</v>
+        <v>-0.247167556574392</v>
       </c>
       <c r="O4" s="5">
         <v>169</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5207326771154123</v>
+        <v>0.5212564061614351</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3295888511720704</v>
+        <v>0.3265401158506894</v>
       </c>
       <c r="R4" s="5">
         <v>166</v>
@@ -6474,16 +6474,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05592502667351549</v>
+        <v>-0.03042412453629595</v>
       </c>
       <c r="O5" s="5">
         <v>184</v>
       </c>
       <c r="P5" s="4">
-        <v>0.30482917627942</v>
+        <v>0.3034009612878041</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2908939632673448</v>
+        <v>0.289727407918616</v>
       </c>
       <c r="R5" s="5">
         <v>184</v>
@@ -6533,16 +6533,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6238024522975589</v>
+        <v>-0.7432307245198331</v>
       </c>
       <c r="O6" s="5">
         <v>165</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2138477979764767</v>
+        <v>0.1983050596779214</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1863292611053726</v>
+        <v>0.1691304367881568</v>
       </c>
       <c r="R6" s="5">
         <v>163</v>
@@ -6592,22 +6592,22 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.09322944406270131</v>
+        <v>-0.1626729705307557</v>
       </c>
       <c r="O7" s="5">
         <v>164</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2156792675031103</v>
+        <v>0.207779971195138</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2156792675031103</v>
+        <v>0.1967824291386226</v>
       </c>
       <c r="R7" s="5">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -6651,16 +6651,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2640213038177466</v>
+        <v>-0.3340433772837299</v>
       </c>
       <c r="O8" s="5">
         <v>141</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3082922408743908</v>
+        <v>0.3083071274721055</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2285642382882155</v>
+        <v>0.2180024995317313</v>
       </c>
       <c r="R8" s="5">
         <v>139</v>
@@ -6710,16 +6710,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.3056804674652357</v>
+        <v>0.273443085785142</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2273899185882041</v>
+        <v>0.2254936020187869</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2273899185882041</v>
+        <v>0.2254936020187869</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -6769,16 +6769,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.4078186718683572</v>
+        <v>-0.4946092644620586</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1465585946613117</v>
+        <v>0.1249184876732174</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1548205659265709</v>
+        <v>0.1302951113400641</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -6951,16 +6951,16 @@
         <v>16</v>
       </c>
       <c r="N3" s="4">
-        <v>1.143980966469009</v>
+        <v>1.162011463604293</v>
       </c>
       <c r="O3" s="5">
         <v>177</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5274549445254729</v>
+        <v>0.5265042581174343</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5044697123524536</v>
+        <v>0.5043150449904873</v>
       </c>
       <c r="R3" s="5">
         <v>174</v>
@@ -7010,16 +7010,16 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>1.151950514719572</v>
+        <v>1.076742782159142</v>
       </c>
       <c r="O4" s="5">
         <v>149</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5862516404384343</v>
+        <v>0.5749637204934825</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4258783877193209</v>
+        <v>0.4176693606828317</v>
       </c>
       <c r="R4" s="5">
         <v>144</v>
@@ -7069,16 +7069,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5777470346134637</v>
+        <v>0.6662218510194293</v>
       </c>
       <c r="O5" s="5">
         <v>160</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4215527309617412</v>
+        <v>0.4250370419007463</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3909957996830365</v>
+        <v>0.3873047647141081</v>
       </c>
       <c r="R5" s="5">
         <v>160</v>
@@ -7128,16 +7128,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.6318994549474084</v>
+        <v>0.6132919618012842</v>
       </c>
       <c r="O6" s="5">
         <v>160</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2684920117386424</v>
+        <v>0.2677100992114279</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2584550494614903</v>
+        <v>0.2582301863286168</v>
       </c>
       <c r="R6" s="5">
         <v>160</v>
@@ -7187,16 +7187,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.3144416375053251</v>
+        <v>0.3511840516433926</v>
       </c>
       <c r="O7" s="5">
         <v>162</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2555195523191537</v>
+        <v>0.2544121229516473</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2526366599390264</v>
+        <v>0.2515155586040199</v>
       </c>
       <c r="R7" s="5">
         <v>162</v>
@@ -7246,16 +7246,16 @@
         <v>5</v>
       </c>
       <c r="N8" s="4">
-        <v>0.7708517581298134</v>
+        <v>0.7356631826149123</v>
       </c>
       <c r="O8" s="5">
         <v>158</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3799635711881203</v>
+        <v>0.3779082682565638</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3842124642157866</v>
+        <v>0.3816857197849078</v>
       </c>
       <c r="R8" s="5">
         <v>158</v>
@@ -7305,16 +7305,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.8115779831141674</v>
+        <v>0.7942188900291445</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.14474364572391</v>
+        <v>0.1437225226012615</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.14474364572391</v>
+        <v>0.1437225226012615</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -7364,16 +7364,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4890058546339126</v>
+        <v>0.432979987493078</v>
       </c>
       <c r="O10" s="5">
         <v>16</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1264422863636588</v>
+        <v>0.1137953884688651</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1341576853759978</v>
+        <v>0.1175932274372568</v>
       </c>
       <c r="R10" s="5">
         <v>16</v>
@@ -7510,13 +7510,13 @@
         <v>2.622061482820977</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6936669009897861</v>
+        <v>0.6883142553523058</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3821326170166501</v>
+        <v>0.3707001332189986</v>
       </c>
       <c r="J3" s="4">
-        <v>1.130149579731896</v>
+        <v>1.129677955561876</v>
       </c>
       <c r="K3" s="4">
         <v>85.92485638016502</v>
@@ -7560,13 +7560,13 @@
         <v>0.9041591320072333</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4574357456938669</v>
+        <v>0.4637346957343995</v>
       </c>
       <c r="I4" s="4">
-        <v>0.307509532537392</v>
+        <v>0.3004294410648121</v>
       </c>
       <c r="J4" s="4">
-        <v>0.5793998898879166</v>
+        <v>0.6010316641735288</v>
       </c>
       <c r="K4" s="4">
         <v>81.20720620978962</v>
@@ -7610,13 +7610,13 @@
         <v>0.27124773960217</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5087479070443248</v>
+        <v>0.5177435685333081</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3338407908690387</v>
+        <v>0.324789624067539</v>
       </c>
       <c r="J5" s="4">
-        <v>0.6036924262261885</v>
+        <v>0.6144737836411703</v>
       </c>
       <c r="K5" s="4">
         <v>81.97724840388241</v>
@@ -7660,13 +7660,13 @@
         <v>0.3616636528028933</v>
       </c>
       <c r="H6" s="4">
-        <v>0.5113337428727973</v>
+        <v>0.4951601924281456</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3353813018352062</v>
+        <v>0.3308627075269506</v>
       </c>
       <c r="J6" s="4">
-        <v>0.6264597677082052</v>
+        <v>0.6003949023238579</v>
       </c>
       <c r="K6" s="4">
         <v>75.33767575746386</v>
@@ -7710,13 +7710,13 @@
         <v>1.35623869801085</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3337159578391688</v>
+        <v>0.3311029956233161</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2720716196139613</v>
+        <v>0.2677203907646864</v>
       </c>
       <c r="J7" s="4">
-        <v>0.3453404623030457</v>
+        <v>0.3435333217802165</v>
       </c>
       <c r="K7" s="4">
         <v>94.64337995596054</v>
@@ -7760,13 +7760,13 @@
         <v>0.1808318264014467</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5034250332391622</v>
+        <v>0.4993703618146187</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3098563464221387</v>
+        <v>0.3049376958093481</v>
       </c>
       <c r="J8" s="4">
-        <v>0.6275144242663407</v>
+        <v>0.6130854951033298</v>
       </c>
       <c r="K8" s="4">
         <v>80.73974978779978</v>
@@ -7792,13 +7792,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>62.29656419529837</v>
+        <v>63.01989150090416</v>
       </c>
       <c r="C9" s="3">
         <v>1.89873417721519</v>
       </c>
       <c r="D9" s="3">
-        <v>35.80470162748644</v>
+        <v>35.08137432188065</v>
       </c>
       <c r="E9" s="3">
         <v>0.09041591320072333</v>
@@ -7807,16 +7807,16 @@
         <v>34.17721518987342</v>
       </c>
       <c r="G9" s="3">
-        <v>1.537070524412296</v>
+        <v>0.81374321880651</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6443442971218065</v>
+        <v>0.641451558216251</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4069052537940125</v>
+        <v>0.4243580613726398</v>
       </c>
       <c r="J9" s="4">
-        <v>0.8063440398228742</v>
+        <v>0.8124685122538877</v>
       </c>
       <c r="K9" s="4">
         <v>68.3960093983344</v>
@@ -7860,13 +7860,13 @@
         <v>0.9945750452079566</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4627000020268764</v>
+        <v>0.4591017319113287</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3582317690268766</v>
+        <v>0.3543444617220855</v>
       </c>
       <c r="J10" s="4">
-        <v>0.5817605411669849</v>
+        <v>0.5824789259741538</v>
       </c>
       <c r="K10" s="4">
         <v>74.57030913631282</v>
@@ -7892,13 +7892,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>66.81735985533453</v>
+        <v>66.90777576853526</v>
       </c>
       <c r="C11" s="3">
         <v>13.01989150090416</v>
       </c>
       <c r="D11" s="3">
-        <v>20.1627486437613</v>
+        <v>20.07233273056058</v>
       </c>
       <c r="E11" s="3">
         <v>0.1808318264014467</v>
@@ -7907,16 +7907,16 @@
         <v>18.9873417721519</v>
       </c>
       <c r="G11" s="3">
-        <v>0.9945750452079566</v>
+        <v>0.9041591320072333</v>
       </c>
       <c r="H11" s="4">
-        <v>0.641965605441344</v>
+        <v>0.6695171755059917</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3274144078259565</v>
+        <v>0.3141689664883179</v>
       </c>
       <c r="J11" s="4">
-        <v>0.8327983063168142</v>
+        <v>0.8734503812297305</v>
       </c>
       <c r="K11" s="4">
         <v>82.96905561501254</v>
@@ -7942,13 +7942,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>87.07052441229656</v>
+        <v>87.16094032549728</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>12.92947558770343</v>
+        <v>12.83905967450271</v>
       </c>
       <c r="E12" s="3">
         <v>4.430379746835443</v>
@@ -7957,16 +7957,16 @@
         <v>6.419529837251356</v>
       </c>
       <c r="G12" s="3">
-        <v>2.079566003616637</v>
+        <v>1.989150090415913</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8429410265140569</v>
+        <v>0.8365456805654184</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3411420076129275</v>
+        <v>0.3348413000365611</v>
       </c>
       <c r="J12" s="4">
-        <v>0.6087276859698062</v>
+        <v>0.6103140798648818</v>
       </c>
       <c r="K12" s="4">
         <v>82.76491247493558</v>
@@ -8010,13 +8010,13 @@
         <v>2.16998191681736</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5135564435132001</v>
+        <v>0.5015632162832524</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3832637038267465</v>
+        <v>0.3727992687961551</v>
       </c>
       <c r="J13" s="4">
-        <v>0.5979171677608571</v>
+        <v>0.6074474858869532</v>
       </c>
       <c r="K13" s="4">
         <v>85.1814161469287</v>
@@ -8060,13 +8060,13 @@
         <v>1.35623869801085</v>
       </c>
       <c r="H14" s="4">
-        <v>0.5661686278859445</v>
+        <v>0.5627706862043984</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3068220844601895</v>
+        <v>0.3003754717701771</v>
       </c>
       <c r="J14" s="4">
-        <v>0.6749048546551731</v>
+        <v>0.6733287077815548</v>
       </c>
       <c r="K14" s="4">
         <v>83.52901920261743</v>
@@ -8110,13 +8110,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.283021911114589</v>
+        <v>0.2817403988847841</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2768172328156137</v>
+        <v>0.2754365451720687</v>
       </c>
       <c r="J15" s="4">
-        <v>0.276957958277931</v>
+        <v>0.2760859722611092</v>
       </c>
       <c r="K15" s="4">
         <v>92.46986136226647</v>
@@ -8142,13 +8142,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>93.85171790235081</v>
+        <v>93.7613019891501</v>
       </c>
       <c r="C16" s="3">
         <v>0.09041591320072333</v>
       </c>
       <c r="D16" s="3">
-        <v>6.057866184448462</v>
+        <v>6.148282097649186</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -8157,16 +8157,16 @@
         <v>5.15370705244123</v>
       </c>
       <c r="G16" s="3">
-        <v>0.9041591320072333</v>
+        <v>0.9945750452079566</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3197971006030852</v>
+        <v>0.3157860708229076</v>
       </c>
       <c r="I16" s="4">
-        <v>0.251932371127147</v>
+        <v>0.2437971211560188</v>
       </c>
       <c r="J16" s="4">
-        <v>0.3181578767395487</v>
+        <v>0.3141625988862574</v>
       </c>
       <c r="K16" s="4">
         <v>94.65546616476598</v>
@@ -8210,13 +8210,13 @@
         <v>0.7233273056057866</v>
       </c>
       <c r="H17" s="4">
-        <v>0.4078308205054866</v>
+        <v>0.4054366507774104</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3625188969158148</v>
+        <v>0.3597955970500431</v>
       </c>
       <c r="J17" s="4">
-        <v>0.3980101007261372</v>
+        <v>0.3979963318439328</v>
       </c>
       <c r="K17" s="4">
         <v>84.51861214648584</v>
@@ -8260,13 +8260,13 @@
         <v>1.62748643761302</v>
       </c>
       <c r="H18" s="4">
-        <v>0.3337239678913677</v>
+        <v>0.3282457062580942</v>
       </c>
       <c r="I18" s="4">
-        <v>0.2841031475244891</v>
+        <v>0.2751819558430005</v>
       </c>
       <c r="J18" s="4">
-        <v>0.3591069584601429</v>
+        <v>0.3583540022814301</v>
       </c>
       <c r="K18" s="4">
         <v>93.48085888966696</v>
@@ -8453,16 +8453,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1010536706882624</v>
+        <v>0.09070041142487595</v>
       </c>
       <c r="O3" s="5">
         <v>189</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3681956480923494</v>
+        <v>0.3673926475709356</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3007718238992763</v>
+        <v>0.2998986156820011</v>
       </c>
       <c r="R3" s="5">
         <v>183</v>
@@ -8512,16 +8512,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1042716341802108</v>
+        <v>-0.02216627982572295</v>
       </c>
       <c r="O4" s="5">
         <v>165</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5053322925851488</v>
+        <v>0.5023317334144346</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4045217342981166</v>
+        <v>0.3834997472834487</v>
       </c>
       <c r="R4" s="5">
         <v>160</v>
@@ -8571,16 +8571,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.163978252575721</v>
+        <v>0.1388790843416245</v>
       </c>
       <c r="O5" s="5">
         <v>175</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3261445128567853</v>
+        <v>0.3261467917703444</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2993157075538557</v>
+        <v>0.29859274822872</v>
       </c>
       <c r="R5" s="5">
         <v>173</v>
@@ -8630,16 +8630,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.42337469590323</v>
+        <v>-0.5105849725977887</v>
       </c>
       <c r="O6" s="5">
         <v>165</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2543847516618264</v>
+        <v>0.2457126950992435</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2257752583503899</v>
+        <v>0.2159267314410936</v>
       </c>
       <c r="R6" s="5">
         <v>163</v>
@@ -8689,16 +8689,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.02164807395665699</v>
+        <v>-0.08219453838446933</v>
       </c>
       <c r="O7" s="5">
         <v>164</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2026053812015191</v>
+        <v>0.1970929372823976</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.191251020038966</v>
+        <v>0.1853333067434831</v>
       </c>
       <c r="R7" s="5">
         <v>163</v>
@@ -8748,16 +8748,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>0.09240800933493315</v>
+        <v>0.006073921971338159</v>
       </c>
       <c r="O8" s="5">
         <v>158</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3382146317973287</v>
+        <v>0.3215374774424369</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3040973762248401</v>
+        <v>0.2869926025275151</v>
       </c>
       <c r="R8" s="5">
         <v>156</v>
@@ -8807,16 +8807,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.283857151094038</v>
+        <v>0.2692129202944793</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2006394320369949</v>
+        <v>0.1997780066958444</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2006394320369949</v>
+        <v>0.1997780066958444</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -8866,16 +8866,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2896452779971051</v>
+        <v>-0.3547360729522526</v>
       </c>
       <c r="O10" s="5">
         <v>15</v>
       </c>
       <c r="P10" s="4">
-        <v>0.140183718870678</v>
+        <v>0.1232687564227212</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1503039245981019</v>
+        <v>0.1311336338237509</v>
       </c>
       <c r="R10" s="5">
         <v>15</v>
@@ -10052,13 +10052,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="C9" s="5">
         <v>21</v>
       </c>
       <c r="D9" s="5">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -10067,7 +10067,7 @@
         <v>378</v>
       </c>
       <c r="G9" s="5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
@@ -10140,13 +10140,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C11" s="5">
         <v>144</v>
       </c>
       <c r="D11" s="5">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E11" s="5">
         <v>2</v>
@@ -10155,7 +10155,7 @@
         <v>210</v>
       </c>
       <c r="G11" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" s="5">
         <v>2</v>
@@ -10184,13 +10184,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
       </c>
       <c r="D12" s="5">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="5">
         <v>49</v>
@@ -10199,7 +10199,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="5">
         <v>48</v>
@@ -10360,13 +10360,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="5">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         <v>57</v>
       </c>
       <c r="G16" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="5">
         <v>0</v>
@@ -10646,16 +10646,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9665985373063286</v>
+        <v>-1.06254047785657</v>
       </c>
       <c r="O3" s="5">
         <v>170</v>
       </c>
       <c r="P3" s="4">
-        <v>0.530555410728542</v>
+        <v>0.5286573362275888</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4227482946778567</v>
+        <v>0.4129072118169998</v>
       </c>
       <c r="R3" s="5">
         <v>165</v>
@@ -10705,16 +10705,16 @@
         <v>25</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.021422437953194</v>
+        <v>-1.008417546054716</v>
       </c>
       <c r="O4" s="5">
         <v>142</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8574204109460647</v>
+        <v>0.8551468454308134</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5530913481691423</v>
+        <v>0.5533177352364705</v>
       </c>
       <c r="R4" s="5">
         <v>137</v>
@@ -10764,16 +10764,16 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2235223258709237</v>
+        <v>-0.2297713197478117</v>
       </c>
       <c r="O5" s="5">
         <v>178</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6436933594755656</v>
+        <v>0.6439309149035164</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4755492778239309</v>
+        <v>0.475372251289886</v>
       </c>
       <c r="R5" s="5">
         <v>174</v>
@@ -10823,16 +10823,16 @@
         <v>65</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.862665495385218</v>
+        <v>-1.966843502552845</v>
       </c>
       <c r="O6" s="5">
         <v>162</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2666017631235744</v>
+        <v>0.2526702071721182</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2308368877016089</v>
+        <v>0.2145166329922768</v>
       </c>
       <c r="R6" s="5">
         <v>160</v>
@@ -10882,16 +10882,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2754543279755522</v>
+        <v>-0.3507663222812285</v>
       </c>
       <c r="O7" s="5">
         <v>161</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2631193012011765</v>
+        <v>0.25326429231152</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.231757228490331</v>
+        <v>0.2201713326361128</v>
       </c>
       <c r="R7" s="5">
         <v>159</v>
@@ -10941,16 +10941,16 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8517890919151284</v>
+        <v>-1.007056895326679</v>
       </c>
       <c r="O8" s="5">
         <v>138</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5009020770709893</v>
+        <v>0.493268324589435</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3952121020063786</v>
+        <v>0.3611340530652851</v>
       </c>
       <c r="R8" s="5">
         <v>133</v>
@@ -11229,16 +11229,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4163409073638946</v>
+        <v>-0.375969515471291</v>
       </c>
       <c r="O3" s="5">
         <v>117</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5515761524828934</v>
+        <v>0.5509835288219977</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3542688010414643</v>
+        <v>0.3510105150005656</v>
       </c>
       <c r="R3" s="5">
         <v>117</v>
@@ -11288,16 +11288,16 @@
         <v>20</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.155195213770989</v>
+        <v>-1.438500709892013</v>
       </c>
       <c r="O4" s="5">
         <v>74</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8430442502003154</v>
+        <v>0.87647434343582</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6822051427822005</v>
+        <v>0.6377152345061811</v>
       </c>
       <c r="R4" s="5">
         <v>71</v>
@@ -11347,16 +11347,16 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3552090846226743</v>
+        <v>-0.4018066980511321</v>
       </c>
       <c r="O5" s="5">
         <v>135</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4550818710612185</v>
+        <v>0.4619289176292603</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3481991488740213</v>
+        <v>0.342796160388278</v>
       </c>
       <c r="R5" s="5">
         <v>131</v>
@@ -11406,16 +11406,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.308077547449258</v>
+        <v>-1.325679212854066</v>
       </c>
       <c r="O6" s="5">
         <v>149</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2204374747918078</v>
+        <v>0.2188372550377638</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1721029666030167</v>
+        <v>0.1715122309965121</v>
       </c>
       <c r="R6" s="5">
         <v>149</v>
@@ -11465,16 +11465,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4538171312136368</v>
+        <v>-0.4845642287740413</v>
       </c>
       <c r="O7" s="5">
         <v>156</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2320349035781678</v>
+        <v>0.2288811873448885</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2314239858440592</v>
+        <v>0.2296853148070427</v>
       </c>
       <c r="R7" s="5">
         <v>156</v>
@@ -11524,16 +11524,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8918344739753193</v>
+        <v>-0.9299083694221384</v>
       </c>
       <c r="O8" s="5">
         <v>145</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3520391957483913</v>
+        <v>0.3503960502468934</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2607738539534303</v>
+        <v>0.2557049101111663</v>
       </c>
       <c r="R8" s="5">
         <v>142</v>
@@ -11583,16 +11583,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>0.6714710753098873</v>
+        <v>0.4494653492085252</v>
       </c>
       <c r="O9" s="5">
         <v>15</v>
       </c>
       <c r="P9" s="4">
-        <v>0.6161788457010207</v>
+        <v>0.6292380060599242</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5242681463461364</v>
+        <v>0.5094677646060455</v>
       </c>
       <c r="R9" s="5">
         <v>15</v>
@@ -11642,16 +11642,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4512882090827422</v>
+        <v>0.4295994212722514</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1979453889496541</v>
+        <v>0.1987692128834765</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1556209385156199</v>
+        <v>0.1500247735643135</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
@@ -11824,16 +11824,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8643462569393875</v>
+        <v>-0.9404715941827533</v>
       </c>
       <c r="O3" s="5">
         <v>104</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5057825211628018</v>
+        <v>0.5112092257076527</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3649714038264433</v>
+        <v>0.3570332363338641</v>
       </c>
       <c r="R3" s="5">
         <v>102</v>
@@ -11883,16 +11883,16 @@
         <v>42</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.687990498812851</v>
+        <v>-1.887420373834232</v>
       </c>
       <c r="O4" s="5">
         <v>111</v>
       </c>
       <c r="P4" s="4">
-        <v>1.031688090624099</v>
+        <v>1.089479338200664</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6316155800372499</v>
+        <v>0.6021022316715875</v>
       </c>
       <c r="R4" s="5">
         <v>111</v>
@@ -11942,16 +11942,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4365683089978644</v>
+        <v>-0.4274613766406787</v>
       </c>
       <c r="O5" s="5">
         <v>165</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6410658393766389</v>
+        <v>0.6399886753343911</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4457893130844429</v>
+        <v>0.4457341195550054</v>
       </c>
       <c r="R5" s="5">
         <v>165</v>
@@ -12001,16 +12001,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.193512000050022</v>
+        <v>-1.213012517294942</v>
       </c>
       <c r="O6" s="5">
         <v>155</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2123123241638591</v>
+        <v>0.2119726421098425</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.212159181839849</v>
+        <v>0.2112943456598978</v>
       </c>
       <c r="R6" s="5">
         <v>155</v>
@@ -12060,16 +12060,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2547398189612475</v>
+        <v>-0.3148225116046888</v>
       </c>
       <c r="O7" s="5">
         <v>155</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2248971365548683</v>
+        <v>0.2193899901975379</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2181301614723827</v>
+        <v>0.2144048287987674</v>
       </c>
       <c r="R7" s="5">
         <v>155</v>
@@ -12119,16 +12119,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7111197719245943</v>
+        <v>-0.827925275865482</v>
       </c>
       <c r="O8" s="5">
         <v>131</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3769383784630131</v>
+        <v>0.3685401356096669</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2338480077081844</v>
+        <v>0.2127296622941379</v>
       </c>
       <c r="R8" s="5">
         <v>130</v>
@@ -12178,16 +12178,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.2934821102026102</v>
+        <v>0.2494398808654523</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2485793908469463</v>
+        <v>0.240814413335242</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2485793908469463</v>
+        <v>0.240814413335242</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -12237,16 +12237,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.09180301957329107</v>
+        <v>-0.1127060680047407</v>
       </c>
       <c r="O10" s="5">
         <v>14</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1212541959696426</v>
+        <v>0.1248963083130347</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08701738247077628</v>
+        <v>0.0869607227952989</v>
       </c>
       <c r="R10" s="5">
         <v>14</v>
@@ -12419,16 +12419,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6540042333465315</v>
+        <v>-0.7948937309781039</v>
       </c>
       <c r="O3" s="5">
         <v>140</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5939955910262023</v>
+        <v>0.5753910783227473</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4554232386783039</v>
+        <v>0.4435541850112454</v>
       </c>
       <c r="R3" s="5">
         <v>140</v>
@@ -12478,16 +12478,16 @@
         <v>29</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.400276473151393</v>
+        <v>-1.261194263647796</v>
       </c>
       <c r="O4" s="5">
         <v>89</v>
       </c>
       <c r="P4" s="4">
-        <v>1.037968325597338</v>
+        <v>0.9805851990087928</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6859294260231305</v>
+        <v>0.6875280721093788</v>
       </c>
       <c r="R4" s="5">
         <v>87</v>
@@ -12537,16 +12537,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5642104792517965</v>
+        <v>-0.5060776831061276</v>
       </c>
       <c r="O5" s="5">
         <v>127</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4922275677888858</v>
+        <v>0.4801808121569495</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3175251389608864</v>
+        <v>0.3153257873330105</v>
       </c>
       <c r="R5" s="5">
         <v>127</v>
@@ -12596,16 +12596,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8227872620222861</v>
+        <v>-0.8463661137733602</v>
       </c>
       <c r="O6" s="5">
         <v>142</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2397710937024731</v>
+        <v>0.2384323637492218</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2062180246829322</v>
+        <v>0.2051606029432615</v>
       </c>
       <c r="R6" s="5">
         <v>142</v>
@@ -12655,16 +12655,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1833194150286342</v>
+        <v>-0.2333132831295264</v>
       </c>
       <c r="O7" s="5">
         <v>142</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2848176885114876</v>
+        <v>0.279386849786473</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2639741774317967</v>
+        <v>0.2612226360945188</v>
       </c>
       <c r="R7" s="5">
         <v>142</v>
@@ -12714,16 +12714,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7847185987690889</v>
+        <v>-0.8620353131373424</v>
       </c>
       <c r="O8" s="5">
         <v>111</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3556940598954951</v>
+        <v>0.3578864854076401</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2193798342174474</v>
+        <v>0.2108281449575402</v>
       </c>
       <c r="R8" s="5">
         <v>109</v>
@@ -12773,16 +12773,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4503030975786949</v>
+        <v>-0.2603036533965604</v>
       </c>
       <c r="O9" s="5">
         <v>15</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2844360299453419</v>
+        <v>0.2956124678384087</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2837095812668606</v>
+        <v>0.2710429516547183</v>
       </c>
       <c r="R9" s="5">
         <v>15</v>
@@ -12832,16 +12832,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.6320576969231981</v>
+        <v>-0.644392003509707</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1317145562912796</v>
+        <v>0.1309891042523661</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.09418188048316228</v>
+        <v>0.09133562680358177</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
@@ -13014,16 +13014,16 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3565736796116128</v>
+        <v>0.3233157892986278</v>
       </c>
       <c r="O3" s="5">
         <v>192</v>
       </c>
       <c r="P3" s="4">
-        <v>0.403232036255195</v>
+        <v>0.4025555564301582</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3261891604489339</v>
+        <v>0.3240464727072965</v>
       </c>
       <c r="R3" s="5">
         <v>187</v>
@@ -13073,16 +13073,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="4">
-        <v>0.463118098680983</v>
+        <v>0.358737374453729</v>
       </c>
       <c r="O4" s="5">
         <v>165</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5376398745274439</v>
+        <v>0.5320607479592243</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3657543816898152</v>
+        <v>0.3523264172974401</v>
       </c>
       <c r="R4" s="5">
         <v>160</v>
@@ -13132,16 +13132,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1767477517619974</v>
+        <v>0.1894144224075944</v>
       </c>
       <c r="O5" s="5">
         <v>185</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2917363167564471</v>
+        <v>0.2916879590050993</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2811732577460079</v>
+        <v>0.2811243743669279</v>
       </c>
       <c r="R5" s="5">
         <v>184</v>
@@ -13191,16 +13191,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.04996581076386056</v>
+        <v>-0.1268707831780755</v>
       </c>
       <c r="O6" s="5">
         <v>165</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2161668563734817</v>
+        <v>0.2088877045775553</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1874637124714709</v>
+        <v>0.1791516266361564</v>
       </c>
       <c r="R6" s="5">
         <v>163</v>
@@ -13250,16 +13250,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.07986037165646551</v>
+        <v>0.04658767296036581</v>
       </c>
       <c r="O7" s="5">
         <v>164</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1923076967974658</v>
+        <v>0.1897525267566605</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1923076967974658</v>
+        <v>0.1897525267566605</v>
       </c>
       <c r="R7" s="5">
         <v>164</v>
@@ -13309,16 +13309,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1554763997158418</v>
+        <v>0.1362916535822096</v>
       </c>
       <c r="O8" s="5">
         <v>157</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3417133804165103</v>
+        <v>0.3417271394011701</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2923021227212309</v>
+        <v>0.2916974627656012</v>
       </c>
       <c r="R8" s="5">
         <v>155</v>
@@ -13368,16 +13368,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5434691301703978</v>
+        <v>0.5894156176855558</v>
       </c>
       <c r="O9" s="5">
         <v>17</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2528116579795726</v>
+        <v>0.2501089234198575</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2528116579795726</v>
+        <v>0.2501089234198575</v>
       </c>
       <c r="R9" s="5">
         <v>17</v>
@@ -13427,16 +13427,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1192436232549036</v>
+        <v>0.09704576355803374</v>
       </c>
       <c r="O10" s="5">
         <v>13</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1148877325588579</v>
+        <v>0.116193489011615</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06285162636133249</v>
+        <v>0.0577290433543625</v>
       </c>
       <c r="R10" s="5">
         <v>13</v>
